--- a/food_beverage_order_forms/026_sub_order_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/026_sub_order_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'stripe',_'label':_'stripe'}</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'stripe', 'label': 'Stripe'}</t>
+          <t>Stripe</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'paypal',_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'paypal', 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cash',_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'cash', 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'stripe',_'label':_'stripe'}</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'stripe', 'label': 'Stripe'}</t>
+          <t>Stripe</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'paypal',_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'paypal', 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cash',_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'cash', 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'processing',_'label':_'processing'}</t>
+          <t>processing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'processing', 'label': 'Processing'}</t>
+          <t>Processing</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'completed',_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'completed', 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sub',_'label':_'sub'}</t>
+          <t>sub</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'sub', 'label': 'Sub'}</t>
+          <t>Sub</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'chips',_'label':_'chips'}</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'chips', 'label': 'Chips'}</t>
+          <t>Chips</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'drink',_'label':_'drink'}</t>
+          <t>drink</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'drink', 'label': 'Drink'}</t>
+          <t>Drink</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'cookie',_'label':_'cookie'}</t>
+          <t>cookie</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'cookie', 'label': 'Cookie'}</t>
+          <t>Cookie</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'small',_'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'small', 'label': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'large',_'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'large', 'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'veggie',_'label':_'veggie'}</t>
+          <t>veggie</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'veggie', 'label': 'Veggie'}</t>
+          <t>Veggie</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'meat',_'label':_'meat'}</t>
+          <t>meat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'meat', 'label': 'Meat'}</t>
+          <t>Meat</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'turkey',_'label':_'turkey'}</t>
+          <t>turkey</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'turkey', 'label': 'Turkey'}</t>
+          <t>Turkey</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'tuna',_'label':_'tuna'}</t>
+          <t>tuna</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'tuna', 'label': 'Tuna'}</t>
+          <t>Tuna</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'chicken',_'label':_'chicken'}</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'chicken', 'label': 'Chicken'}</t>
+          <t>Chicken</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'fish',_'label':_'fish'}</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'fish', 'label': 'Fish'}</t>
+          <t>Fish</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'whole_wheat',_'label':_'whole_wheat'}</t>
+          <t>whole_wheat</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'whole_wheat', 'label': 'Whole Wheat'}</t>
+          <t>Whole Wheat</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'white',_'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'white', 'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rye',_'label':_'rye'}</t>
+          <t>rye</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'rye', 'label': 'Rye'}</t>
+          <t>Rye</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'gluten_free',_'label':_'gluten_free'}</t>
+          <t>gluten_free</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'gluten_free', 'label': 'Gluten Free'}</t>
+          <t>Gluten Free</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'mayonnaise',_'label':_'mayonnaise'}</t>
+          <t>mayonnaise</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'mayonnaise', 'label': 'Mayonnaise'}</t>
+          <t>Mayonnaise</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'mustard',_'label':_'mustard'}</t>
+          <t>mustard</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'mustard', 'label': 'Mustard'}</t>
+          <t>Mustard</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'ketchup',_'label':_'ketchup'}</t>
+          <t>ketchup</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'ketchup', 'label': 'Ketchup'}</t>
+          <t>Ketchup</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'relish',_'label':_'relish'}</t>
+          <t>relish</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'relish', 'label': 'Relish'}</t>
+          <t>Relish</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'ranch',_'label':_'ranch'}</t>
+          <t>ranch</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'ranch', 'label': 'Ranch'}</t>
+          <t>Ranch</t>
         </is>
       </c>
     </row>
